--- a/data/gebze/service_status.xlsx
+++ b/data/gebze/service_status.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,6 +458,232 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>GDM1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2026-03-22 01:28:31</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>GDM2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2026-03-22 01:28:31</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>GDM3</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2026-03-22 01:28:31</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>GDM4</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2026-03-22 01:28:31</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>GDM5</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2026-03-22 01:28:31</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>GDM6</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2026-03-22 01:28:32</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>GDM7</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2026-03-22 01:28:32</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gebze/service_status.xlsx
+++ b/data/gebze/service_status.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -666,8 +666,6 @@
           <t>Servis</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>Toplu servise alındı</t>
@@ -679,6 +677,241 @@
         </is>
       </c>
       <c r="H8" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>GDM1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Servis Dışı</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Pantograf</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Pantograf Esnek Halat</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2026-04-06 01:04:38</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>GDM2</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Servis Dışı</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Traction_Converter</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Fren Rezistörü</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2026-04-06 01:11:13</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>GDM3</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2026-04-06 01:04:29</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>GDM4</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2026-04-06 01:04:29</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>GDM5</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2026-04-06 01:04:29</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>GDM6</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2026-04-06 01:04:29</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>GDM7</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2026-04-06 01:04:30</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
         <is>
           <t>admin</t>
         </is>

--- a/data/gebze/service_status.xlsx
+++ b/data/gebze/service_status.xlsx
@@ -705,12 +705,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Pantograf Esnek Halat</t>
+          <t>Pantograf Motoru</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-04-06 01:04:38</t>
+          <t>2026-04-06 10:38:13</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -732,23 +732,19 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Servis Dışı</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Traction_Converter</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Fren Rezistörü</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
+          <t>İşletme Kaynaklı Servis Dışı</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Bakım</t>
+        </is>
+      </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-04-06 01:11:13</t>
+          <t>2026-04-06 10:41:53</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -780,7 +776,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-04-06 01:04:29</t>
+          <t>2026-04-06 10:37:12</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -812,7 +808,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-04-06 01:04:29</t>
+          <t>2026-04-06 10:37:12</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -844,7 +840,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-04-06 01:04:29</t>
+          <t>2026-04-06 10:37:12</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -876,7 +872,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-04-06 01:04:29</t>
+          <t>2026-04-06 10:37:12</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -908,7 +904,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-04-06 01:04:30</t>
+          <t>2026-04-06 10:37:12</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
